--- a/AAII_Financials/Quarterly/BVNRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVNRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="92">
   <si>
     <t>BVNRY</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,8 +756,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -799,18 +803,18 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>191500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>145400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>78300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,8 +827,11 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -867,18 +874,18 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>50800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>55600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>63000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,8 +898,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,18 +945,18 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>140700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>89800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>15400</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +998,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1029,18 +1043,18 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3">
         <v>79200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>52200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,8 +1138,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1180,8 +1200,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1189,8 +1209,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1256,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,8 +1306,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1324,18 +1351,18 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>160200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>126900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>110100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,8 +1375,11 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1392,18 +1422,18 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>31300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-31800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,8 +1475,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1486,18 +1520,18 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-8100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-14700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,8 +1544,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1578,8 +1615,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1622,18 +1662,18 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,8 +1686,11 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1690,18 +1733,18 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>23100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-34400</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1757,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1758,18 +1804,18 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,8 +1899,11 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1894,18 +1946,18 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>22200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,8 +1970,11 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1962,18 +2017,18 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>22200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-34600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2098,8 +2159,8 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,8 +2325,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2302,18 +2372,18 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>8100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>14700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,8 +2396,11 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2370,18 +2443,18 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>22200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,8 +2538,11 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2506,18 +2585,18 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>22200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,56 +2741,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E41" s="3">
         <v>106900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>269500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>328800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>192200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>149100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>117300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>124500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>219100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>146400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>121900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>185500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>85400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,56 +2810,59 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E42" s="3">
         <v>246700</v>
       </c>
-      <c r="E42" s="3">
-        <v>256100</v>
-      </c>
       <c r="F42" s="3">
+        <v>254600</v>
+      </c>
+      <c r="G42" s="3">
         <v>139100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>69700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>78900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>76700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>131000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>204100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>207100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>67500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>81300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>248100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>336900</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,56 +2881,59 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>239500</v>
+      </c>
+      <c r="E43" s="3">
         <v>144400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>132900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>195600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>149400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>175400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>169300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>159200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>158300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>271000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>167500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>195200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>114000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>79300</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,56 +2952,59 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>409700</v>
+      </c>
+      <c r="E44" s="3">
         <v>410800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>395200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>395500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>416600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>357800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>323100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>326700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>286300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>257900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>243800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>246800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>221100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>175500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>136400</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,56 +3023,59 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
-        <v>20400</v>
-      </c>
       <c r="H45" s="3">
+        <v>20300</v>
+      </c>
+      <c r="I45" s="3">
         <v>4500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>4500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>27600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,56 +3094,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1022300</v>
+      </c>
+      <c r="E46" s="3">
         <v>920600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1059200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1082000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>868300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>735800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>803400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>776200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>774500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>696700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>801300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>632800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>647200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>747100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>665600</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,8 +3165,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3107,8 +3212,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3131,56 +3236,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>327400</v>
+      </c>
+      <c r="E48" s="3">
         <v>334300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>341000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>343900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>346000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>316000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>311300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>345800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>338200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>343900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>363700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>337800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>355300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>254600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>260000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,56 +3307,59 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>885600</v>
+      </c>
+      <c r="E49" s="3">
         <v>906600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>936900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>945900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>965000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>903800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>878900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>960000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>934900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>926300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>961200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>927000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1158600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>887200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>882100</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3267,8 +3378,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,56 +3520,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E52" s="3">
         <v>14100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31600</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,56 +3662,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2249800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2175500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2351000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2381600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2189300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1963700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1999900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2086200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2050900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1970000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2128500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1900500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2197700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1922200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1839200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,56 +3789,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E57" s="3">
         <v>53900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>152100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>172500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>173700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>145100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>161600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>69500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>141500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>112600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>112000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>89900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,56 +3858,59 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5800</v>
       </c>
       <c r="I58" s="3">
         <v>5800</v>
       </c>
       <c r="J58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>167700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,56 +3929,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E59" s="3">
         <v>39600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>37600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>155100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>198400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>318200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>325000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>322400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>264900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>281000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>175700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>81800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,56 +4000,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E60" s="3">
         <v>142300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>251100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>282000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>259600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>261900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>388300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>460500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>524300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>424500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>413400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>409500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>428900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>260900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>339500</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,56 +4071,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E61" s="3">
         <v>14400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3999,8 +4142,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4028,27 +4174,27 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>46400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>150800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>145500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>325700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>322300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>429100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,56 +4426,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E66" s="3">
         <v>218100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>327700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>314300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>292400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>289300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>416100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>488100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>551400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>498500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>595200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>576300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>778000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>592100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>778000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,56 +4808,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1856900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1794100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1857800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1895900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1713600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1523600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1448500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1446600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1359300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1333600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1383600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1195200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1285000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1199600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>955300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,56 +5092,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2019800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1957400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2023300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2067300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1897000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1674400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1583800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1598100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1499500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1471500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1533400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1324200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1419700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1330200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1061300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,8 +5310,11 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5162,18 +5357,18 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>22200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,53 +5410,54 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E83" s="3">
         <v>10800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5274,14 +5473,17 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,53 +5834,56 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-116000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>85700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>203300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>199900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-56100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>132600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>90600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>62900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>86800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>64900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5682,14 +5899,17 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,53 +5934,54 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7200</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>10500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,53 +6145,56 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-143600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-77000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-111500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-54100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-45200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>22500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-93500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-151100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-151300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>48300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5980,14 +6210,17 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6245,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6056,8 +6290,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,8 +6527,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6293,44 +6539,44 @@
         <v>-35600</v>
       </c>
       <c r="E100" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-23300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>22000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>85200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6346,59 +6592,62 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
-      </c>
-      <c r="N101" s="3">
-        <v>600</v>
       </c>
       <c r="O101" s="3">
         <v>600</v>
       </c>
       <c r="P101" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6414,59 +6663,62 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-157600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-59500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>137000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>83300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-135000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>87000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>27000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-89200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>66000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>28400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-64500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>101500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6482,10 +6734,13 @@
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>
